--- a/examens.xlsx
+++ b/examens.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Desktop/Projet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB37AC9E-898B-40A4-B49A-617E84A84E8A}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE8A53A-9779-4BB3-B540-5D44E21A7F7F}"/>
   <bookViews>
     <workbookView xWindow="5985" yWindow="4050" windowWidth="21600" windowHeight="11235" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>Deutsch</t>
   </si>
   <si>
-    <t>15h30-17h00</t>
-  </si>
-  <si>
     <t>Martin Pfeuti</t>
   </si>
   <si>
@@ -80,13 +77,16 @@
     <t>Français</t>
   </si>
   <si>
-    <t>08h00-09h00</t>
-  </si>
-  <si>
     <t>Patrick Brunner</t>
   </si>
   <si>
     <t>Elisabeth Vick</t>
+  </si>
+  <si>
+    <t>15:30-17:00</t>
+  </si>
+  <si>
+    <t>08:00-09:00</t>
   </si>
 </sst>
 </file>
@@ -518,13 +518,13 @@
         <v>46188</v>
       </c>
       <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -532,25 +532,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>46190</v>
       </c>
       <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Desktop/Projet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BE8A53A-9779-4BB3-B540-5D44E21A7F7F}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD9F27F-8D5C-431F-BE7E-B43B1A32E6DB}"/>
   <bookViews>
     <workbookView xWindow="5985" yWindow="4050" windowWidth="21600" windowHeight="11235" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
@@ -65,6 +65,9 @@
     <t>Deutsch</t>
   </si>
   <si>
+    <t>15h30-17h00</t>
+  </si>
+  <si>
     <t>Martin Pfeuti</t>
   </si>
   <si>
@@ -77,16 +80,13 @@
     <t>Français</t>
   </si>
   <si>
+    <t>08h00-09h00</t>
+  </si>
+  <si>
     <t>Patrick Brunner</t>
   </si>
   <si>
     <t>Elisabeth Vick</t>
-  </si>
-  <si>
-    <t>15:30-17:00</t>
-  </si>
-  <si>
-    <t>08:00-09:00</t>
   </si>
 </sst>
 </file>
@@ -478,10 +478,9 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="1" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -518,13 +517,13 @@
         <v>46188</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -532,25 +531,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>46190</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Desktop/Projet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD9F27F-8D5C-431F-BE7E-B43B1A32E6DB}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{584789C6-C1A3-407E-A54C-1745878A3132}"/>
   <bookViews>
-    <workbookView xWindow="5985" yWindow="4050" windowWidth="21600" windowHeight="11235" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="48">
   <si>
     <t>Klasse</t>
   </si>
@@ -59,34 +59,127 @@
     <t>Sprache</t>
   </si>
   <si>
-    <t>MDM2026</t>
-  </si>
-  <si>
     <t>Deutsch</t>
   </si>
   <si>
-    <t>15h30-17h00</t>
-  </si>
-  <si>
-    <t>Martin Pfeuti</t>
-  </si>
-  <si>
-    <t>Roger Käser</t>
-  </si>
-  <si>
-    <t>MP2025</t>
-  </si>
-  <si>
-    <t>Français</t>
-  </si>
-  <si>
-    <t>08h00-09h00</t>
-  </si>
-  <si>
-    <t>Patrick Brunner</t>
-  </si>
-  <si>
-    <t>Elisabeth Vick</t>
+    <t>BM12023a</t>
+  </si>
+  <si>
+    <t>BM12023c</t>
+  </si>
+  <si>
+    <t>BM12023e</t>
+  </si>
+  <si>
+    <t>BM12023d</t>
+  </si>
+  <si>
+    <t>MP12023a</t>
+  </si>
+  <si>
+    <t>BM12022a</t>
+  </si>
+  <si>
+    <t>BM12022b</t>
+  </si>
+  <si>
+    <t>BM12022c</t>
+  </si>
+  <si>
+    <t>BM12022g</t>
+  </si>
+  <si>
+    <t>MP12022a</t>
+  </si>
+  <si>
+    <t>BM12021a</t>
+  </si>
+  <si>
+    <t>BM12021c</t>
+  </si>
+  <si>
+    <t>BM12021h</t>
+  </si>
+  <si>
+    <t>BILI DE/EN</t>
+  </si>
+  <si>
+    <t>Französisch</t>
+  </si>
+  <si>
+    <t>Capano Maria Chiara</t>
+  </si>
+  <si>
+    <t>Binggeli Christoph</t>
+  </si>
+  <si>
+    <t>Formisano Roberto Ciro</t>
+  </si>
+  <si>
+    <t>Michel Tamara</t>
+  </si>
+  <si>
+    <t>Horsch Lukas</t>
+  </si>
+  <si>
+    <t>Wirz Jonas</t>
+  </si>
+  <si>
+    <t>Hmamda Abdelaziz</t>
+  </si>
+  <si>
+    <t>Mettler Laura</t>
+  </si>
+  <si>
+    <t>Peitrequin Sandra</t>
+  </si>
+  <si>
+    <t>Graf Georg</t>
+  </si>
+  <si>
+    <t>Käser Roger</t>
+  </si>
+  <si>
+    <t>Sellaiah Ratheban</t>
+  </si>
+  <si>
+    <t>von Arx Ursula</t>
+  </si>
+  <si>
+    <t>Gallus Matthias</t>
+  </si>
+  <si>
+    <t>Ellenberger David Severin</t>
+  </si>
+  <si>
+    <t>Wettstein Adrian</t>
+  </si>
+  <si>
+    <t>Huguelet Catherine</t>
+  </si>
+  <si>
+    <t>2. Landessprache</t>
+  </si>
+  <si>
+    <t>Mathematik Grundlagen</t>
+  </si>
+  <si>
+    <t>Englisch</t>
+  </si>
+  <si>
+    <t>1. Landessprache</t>
+  </si>
+  <si>
+    <t>Mathematik Schwerpunkt</t>
+  </si>
+  <si>
+    <t>Naturwissenschaften</t>
+  </si>
+  <si>
+    <t>Rechnungswesen</t>
+  </si>
+  <si>
+    <t>Wirtschaft und Recht</t>
   </si>
 </sst>
 </file>
@@ -122,9 +215,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,12 +570,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF889997-EE60-4F97-AC79-CD858849BFAF}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="7" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -507,49 +603,601 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C2" s="1">
-        <v>46188</v>
-      </c>
-      <c r="D2" t="s">
+        <v>45821</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.0833333333333402E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.3333333333333398E-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.14583333333333301</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1">
-        <v>46190</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.27083333333333298</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45800.361111111109</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45818.361111111109</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45819.375</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.0833333333332999E-2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45821</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45800.361111111109</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45819.541666666664</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8.3333333333332996E-2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45820.395833333336</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45824</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45819.541666666664</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.14583333333333301</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45820.395833333336</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{584789C6-C1A3-407E-A54C-1745878A3132}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35ADDF60-935A-4E6F-AFA2-9C8A65FD6BA8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="64">
   <si>
     <t>Klasse</t>
   </si>
@@ -180,6 +180,54 @@
   </si>
   <si>
     <t>Wirtschaft und Recht</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
   </si>
 </sst>
 </file>
@@ -215,11 +263,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -244,7 +291,7 @@
     <tableColumn id="1" xr3:uid="{564251C1-BA4D-4494-AF7C-B4E1B17C3481}" name="Klasse"/>
     <tableColumn id="2" xr3:uid="{9E6669FF-4668-48FC-BA93-13464AB8E2FD}" name="Prüfung"/>
     <tableColumn id="3" xr3:uid="{98117DAB-AC8E-45B6-A4B9-E90E7B8D66E6}" name="Prüfungsdatum"/>
-    <tableColumn id="4" xr3:uid="{14879760-43D0-4240-87AC-F3EE02A32C04}" name="Prüfungszeit"/>
+    <tableColumn id="8" xr3:uid="{AFDD24F5-D99F-4CAA-B447-86CFAC9B0115}" name="Prüfungszeit"/>
     <tableColumn id="5" xr3:uid="{2E2E62BD-E7F4-4B79-95CB-2132693A6D70}" name="Lehrperson der Klasse"/>
     <tableColumn id="6" xr3:uid="{C5FE5A08-B130-4ADB-9BDF-AD793602DF29}" name="Aufsichtsperson"/>
     <tableColumn id="7" xr3:uid="{0B5FAC31-48CA-42B3-BB6B-BB797C947C6A}" name="Sprache"/>
@@ -574,7 +621,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
@@ -612,8 +659,8 @@
       <c r="C2" s="1">
         <v>45821</v>
       </c>
-      <c r="D2" s="3">
-        <v>0.64583333333333337</v>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -635,8 +682,8 @@
       <c r="C3" s="1">
         <v>45821</v>
       </c>
-      <c r="D3" s="3">
-        <v>0.33333333333333331</v>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -658,8 +705,8 @@
       <c r="C4" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D4" s="3">
-        <v>2.0833333333333402E-2</v>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -681,8 +728,8 @@
       <c r="C5" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D5" s="3">
-        <v>0.70833333333333304</v>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -704,8 +751,8 @@
       <c r="C6" s="1">
         <v>45820</v>
       </c>
-      <c r="D6" s="3">
-        <v>0.39583333333333298</v>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -727,8 +774,8 @@
       <c r="C7" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D7" s="3">
-        <v>8.3333333333333398E-2</v>
+      <c r="D7" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -750,8 +797,8 @@
       <c r="C8" s="1">
         <v>45820</v>
       </c>
-      <c r="D8" s="3">
-        <v>0.77083333333333304</v>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -773,8 +820,8 @@
       <c r="C9" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D9" s="3">
-        <v>0.45833333333333298</v>
+      <c r="D9" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
@@ -796,8 +843,8 @@
       <c r="C10" s="1">
         <v>45821</v>
       </c>
-      <c r="D10" s="3">
-        <v>0.14583333333333301</v>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -819,8 +866,8 @@
       <c r="C11" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D11" s="3">
-        <v>0.83333333333333304</v>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -842,8 +889,8 @@
       <c r="C12" s="1">
         <v>45820</v>
       </c>
-      <c r="D12" s="3">
-        <v>0.52083333333333304</v>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -865,8 +912,8 @@
       <c r="C13" s="1">
         <v>45821</v>
       </c>
-      <c r="D13" s="3">
-        <v>0.20833333333333301</v>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -888,8 +935,8 @@
       <c r="C14" s="1">
         <v>45821</v>
       </c>
-      <c r="D14" s="3">
-        <v>0.89583333333333304</v>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -911,8 +958,8 @@
       <c r="C15" s="1">
         <v>45820</v>
       </c>
-      <c r="D15" s="3">
-        <v>0.58333333333333304</v>
+      <c r="D15" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -934,8 +981,8 @@
       <c r="C16" s="1">
         <v>45821</v>
       </c>
-      <c r="D16" s="3">
-        <v>0.27083333333333298</v>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E16" t="s">
         <v>32</v>
@@ -957,8 +1004,8 @@
       <c r="C17" s="1">
         <v>45800.361111111109</v>
       </c>
-      <c r="D17" s="3">
-        <v>0.95833333333333304</v>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
@@ -980,8 +1027,8 @@
       <c r="C18" s="1">
         <v>45820</v>
       </c>
-      <c r="D18" s="3">
-        <v>0.64583333333333304</v>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -1003,8 +1050,8 @@
       <c r="C19" s="1">
         <v>45818.361111111109</v>
       </c>
-      <c r="D19" s="3">
-        <v>0.33333333333333298</v>
+      <c r="D19" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -1026,8 +1073,8 @@
       <c r="C20" s="1">
         <v>45819.375</v>
       </c>
-      <c r="D20" s="3">
-        <v>2.0833333333332999E-2</v>
+      <c r="D20" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="E20" t="s">
         <v>34</v>
@@ -1049,8 +1096,8 @@
       <c r="C21" s="1">
         <v>45821</v>
       </c>
-      <c r="D21" s="3">
-        <v>0.70833333333333304</v>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E21" t="s">
         <v>35</v>
@@ -1072,8 +1119,8 @@
       <c r="C22" s="1">
         <v>45800.361111111109</v>
       </c>
-      <c r="D22" s="3">
-        <v>0.39583333333333298</v>
+      <c r="D22" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
@@ -1095,8 +1142,8 @@
       <c r="C23" s="1">
         <v>45819.541666666664</v>
       </c>
-      <c r="D23" s="3">
-        <v>8.3333333333332996E-2</v>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>36</v>
@@ -1118,8 +1165,8 @@
       <c r="C24" s="1">
         <v>45820.395833333336</v>
       </c>
-      <c r="D24" s="3">
-        <v>0.77083333333333304</v>
+      <c r="D24" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>37</v>
@@ -1141,8 +1188,8 @@
       <c r="C25" s="1">
         <v>45824</v>
       </c>
-      <c r="D25" s="3">
-        <v>0.45833333333333298</v>
+      <c r="D25" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E25" t="s">
         <v>38</v>
@@ -1164,8 +1211,8 @@
       <c r="C26" s="1">
         <v>45819.541666666664</v>
       </c>
-      <c r="D26" s="3">
-        <v>0.14583333333333301</v>
+      <c r="D26" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
@@ -1187,8 +1234,8 @@
       <c r="C27" s="1">
         <v>45820.395833333336</v>
       </c>
-      <c r="D27" s="3">
-        <v>0.83333333333333304</v>
+      <c r="D27" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E27" t="s">
         <v>37</v>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35ADDF60-935A-4E6F-AFA2-9C8A65FD6BA8}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E189B3-CCCC-4031-B8A5-1A08DAB91C98}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
+    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="48">
   <si>
     <t>Klasse</t>
   </si>
@@ -50,12 +50,6 @@
     <t>Prüfungszeit</t>
   </si>
   <si>
-    <t>Lehrperson der Klasse</t>
-  </si>
-  <si>
-    <t>Aufsichtsperson</t>
-  </si>
-  <si>
     <t>Sprache</t>
   </si>
   <si>
@@ -107,57 +101,6 @@
     <t>Französisch</t>
   </si>
   <si>
-    <t>Capano Maria Chiara</t>
-  </si>
-  <si>
-    <t>Binggeli Christoph</t>
-  </si>
-  <si>
-    <t>Formisano Roberto Ciro</t>
-  </si>
-  <si>
-    <t>Michel Tamara</t>
-  </si>
-  <si>
-    <t>Horsch Lukas</t>
-  </si>
-  <si>
-    <t>Wirz Jonas</t>
-  </si>
-  <si>
-    <t>Hmamda Abdelaziz</t>
-  </si>
-  <si>
-    <t>Mettler Laura</t>
-  </si>
-  <si>
-    <t>Peitrequin Sandra</t>
-  </si>
-  <si>
-    <t>Graf Georg</t>
-  </si>
-  <si>
-    <t>Käser Roger</t>
-  </si>
-  <si>
-    <t>Sellaiah Ratheban</t>
-  </si>
-  <si>
-    <t>von Arx Ursula</t>
-  </si>
-  <si>
-    <t>Gallus Matthias</t>
-  </si>
-  <si>
-    <t>Ellenberger David Severin</t>
-  </si>
-  <si>
-    <t>Wettstein Adrian</t>
-  </si>
-  <si>
-    <t>Huguelet Catherine</t>
-  </si>
-  <si>
     <t>2. Landessprache</t>
   </si>
   <si>
@@ -228,16 +171,31 @@
   </si>
   <si>
     <t>10:00</t>
+  </si>
+  <si>
+    <t>Art der Prüfung</t>
+  </si>
+  <si>
+    <t>mündlich</t>
+  </si>
+  <si>
+    <t>schriftlich</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -271,7 +229,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -285,15 +247,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC9B2745-A68A-429E-8C10-29F527B8AEA0}" name="Tableau1" displayName="Tableau1" ref="A1:G1048576" totalsRowShown="0">
-  <autoFilter ref="A1:G1048576" xr:uid="{CC9B2745-A68A-429E-8C10-29F527B8AEA0}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC9B2745-A68A-429E-8C10-29F527B8AEA0}" name="Tableau1" displayName="Tableau1" ref="A1:F1048576" totalsRowShown="0">
+  <autoFilter ref="A1:F1048576" xr:uid="{CC9B2745-A68A-429E-8C10-29F527B8AEA0}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{564251C1-BA4D-4494-AF7C-B4E1B17C3481}" name="Klasse"/>
     <tableColumn id="2" xr3:uid="{9E6669FF-4668-48FC-BA93-13464AB8E2FD}" name="Prüfung"/>
     <tableColumn id="3" xr3:uid="{98117DAB-AC8E-45B6-A4B9-E90E7B8D66E6}" name="Prüfungsdatum"/>
     <tableColumn id="8" xr3:uid="{AFDD24F5-D99F-4CAA-B447-86CFAC9B0115}" name="Prüfungszeit"/>
-    <tableColumn id="5" xr3:uid="{2E2E62BD-E7F4-4B79-95CB-2132693A6D70}" name="Lehrperson der Klasse"/>
-    <tableColumn id="6" xr3:uid="{C5FE5A08-B130-4ADB-9BDF-AD793602DF29}" name="Aufsichtsperson"/>
+    <tableColumn id="6" xr3:uid="{5DAF50C5-25EA-4171-8C85-3A1A8639D6E0}" name="Art der Prüfung" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{0B5FAC31-48CA-42B3-BB6B-BB797C947C6A}" name="Sprache"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -617,16 +578,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF889997-EE60-4F97-AC79-CD858849BFAF}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -640,614 +602,534 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1">
         <v>45821</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1">
         <v>45821</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>45820</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <v>45820</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C10" s="1">
         <v>45821</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C11" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
         <v>45820</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1">
         <v>45821</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
         <v>45821</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1">
         <v>45820</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
         <v>45821</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>45800.361111111109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
         <v>45820</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1">
         <v>45819.375</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
         <v>45821</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
         <v>45800.361111111109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1">
         <v>45819.541666666664</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1">
         <v>45820.395833333336</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1">
         <v>45824</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1">
         <v>45819.541666666664</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1">
         <v>45820.395833333336</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/olivier_greder_bbz-cfp_ch/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E189B3-CCCC-4031-B8A5-1A08DAB91C98}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FB09ED-CDF1-4523-9FA1-BDDA8EA7E831}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>BILI DE/EN</t>
   </si>
   <si>
-    <t>Französisch</t>
-  </si>
-  <si>
     <t>2. Landessprache</t>
   </si>
   <si>
@@ -180,6 +177,9 @@
   </si>
   <si>
     <t>schriftlich</t>
+  </si>
+  <si>
+    <t>Français</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -613,16 +613,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1">
         <v>45821</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>5</v>
@@ -633,16 +633,16 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1">
         <v>45821</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
@@ -653,16 +653,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>5</v>
@@ -673,16 +673,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>5</v>
@@ -693,16 +693,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>45820</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>5</v>
@@ -713,16 +713,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>5</v>
@@ -733,16 +733,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>45820</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -753,16 +753,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -773,19 +773,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
         <v>45821</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -793,19 +793,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,16 +813,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>45820</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>5</v>
@@ -833,16 +833,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1">
         <v>45821</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>5</v>
@@ -853,16 +853,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>45821</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>5</v>
@@ -873,16 +873,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>45820</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -893,19 +893,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1">
         <v>45821</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -913,16 +913,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1">
         <v>45800.361111111109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>5</v>
@@ -933,16 +933,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
         <v>45820</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>5</v>
@@ -953,16 +953,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1">
         <v>45818.361111111109</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>5</v>
@@ -973,16 +973,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="1">
         <v>45819.375</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>5</v>
@@ -993,16 +993,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1">
         <v>45821</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>5</v>
@@ -1013,16 +1013,16 @@
         <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
         <v>45800.361111111109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>5</v>
@@ -1033,16 +1033,16 @@
         <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>45819.541666666664</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>5</v>
@@ -1053,16 +1053,16 @@
         <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <v>45820.395833333336</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>5</v>
@@ -1073,16 +1073,16 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1">
         <v>45824</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>5</v>
@@ -1093,16 +1093,16 @@
         <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1">
         <v>45819.541666666664</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>5</v>
@@ -1113,16 +1113,16 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1">
         <v>45820.395833333336</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>5</v>

--- a/examens.xlsx
+++ b/examens.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe.sharepoint.com/sites/BBZBM/sekr/7 Abschlussprüfungen/08 Prüfungssoftware/App Prüfungsdaten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00CD8735-E38A-43F1-A604-A65D423485BF}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{E8E93866-4FC7-4153-8862-A8B71A51A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A52EDA6-2123-4754-8BD7-B1A4C74C0A1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A16735CD-65AF-49DB-A76E-C0162408D859}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="50">
   <si>
     <t>Klasse</t>
   </si>
@@ -246,13 +246,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -651,7 +648,7 @@
       <c r="C2" s="2">
         <v>46555</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -731,7 +728,7 @@
       <c r="C6" s="2">
         <v>46555</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -771,7 +768,7 @@
       <c r="C8" s="2">
         <v>46555</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -971,7 +968,7 @@
       <c r="C18" s="2">
         <v>46555</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1091,7 +1088,7 @@
       <c r="C24" s="2">
         <v>46412</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -1111,7 +1108,7 @@
       <c r="C25" s="2">
         <v>46555</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1191,7 +1188,7 @@
       <c r="C29" s="2">
         <v>46412</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1211,7 +1208,7 @@
       <c r="C30" s="2">
         <v>46555</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1291,7 +1288,7 @@
       <c r="C34" s="2">
         <v>46412</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1311,7 +1308,7 @@
       <c r="C35" s="2">
         <v>46555</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1368,7 +1365,12 @@
       <c r="B38" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="3"/>
+      <c r="C38" s="2">
+        <v>46535</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="E38" s="1" t="s">
         <v>13</v>
       </c>
@@ -1426,7 +1428,7 @@
       <c r="C41" s="2">
         <v>46412</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -1446,7 +1448,7 @@
       <c r="C42" s="2">
         <v>46555</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -1526,7 +1528,7 @@
       <c r="C46" s="2">
         <v>46412</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -1546,7 +1548,7 @@
       <c r="C47" s="2">
         <v>46555</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -1586,7 +1588,7 @@
       <c r="C49" s="2">
         <v>46412</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -1606,7 +1608,7 @@
       <c r="C50" s="2">
         <v>46555</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -1797,22 +1799,22 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="4"/>
+      <c r="D60" s="3"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="4"/>
+      <c r="D61" s="3"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="4"/>
+      <c r="D63" s="3"/>
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D64" s="4"/>
+      <c r="D64" s="3"/>
       <c r="F64" s="1"/>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.25">
@@ -1828,6 +1830,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d11981de-575b-46ec-bdf5-eef20d9bab8d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3fadfec4-7fe0-4489-bc25-d6d9f373486a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101007315D4FAD493504B9C1581EC20D09E1B" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b56f164e85a7c147bc867fffc989dd35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d11981de-575b-46ec-bdf5-eef20d9bab8d" xmlns:ns3="3fadfec4-7fe0-4489-bc25-d6d9f373486a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="96f5e66db50345c59b2cae99c36aa41b" ns2:_="" ns3:_="">
     <xsd:import namespace="d11981de-575b-46ec-bdf5-eef20d9bab8d"/>
@@ -2040,17 +2053,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d11981de-575b-46ec-bdf5-eef20d9bab8d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3fadfec4-7fe0-4489-bc25-d6d9f373486a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2061,6 +2063,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C47861C-81B3-4C02-9746-40B2C9411634}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d11981de-575b-46ec-bdf5-eef20d9bab8d"/>
+    <ds:schemaRef ds:uri="3fadfec4-7fe0-4489-bc25-d6d9f373486a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34AAB0B7-0CB4-429B-8A89-E8C04E9DA511}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2079,17 +2092,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C47861C-81B3-4C02-9746-40B2C9411634}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d11981de-575b-46ec-bdf5-eef20d9bab8d"/>
-    <ds:schemaRef ds:uri="3fadfec4-7fe0-4489-bc25-d6d9f373486a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D28C14F2-C2D5-40D2-ADB3-7562A845F73E}">
   <ds:schemaRefs>
